--- a/Data/tables/resources_info.xlsx
+++ b/Data/tables/resources_info.xlsx
@@ -441,126 +441,126 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>vgr_1</t>
+          <t>hbw_1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1866</v>
+        <v>873</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>/vgr/pick_up_and_transport</t>
+          <t>/hbw/get_empty_bucket, /hbw/store, /hbw/store_empty_bucket, /hbw/unload</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mm_1</t>
+          <t>ov_2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>576</v>
+        <v>330</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
+          <t>/ov/burn</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mm_2</t>
+          <t>pm_1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>381</v>
+        <v>204</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
+          <t>/pm/punch_gill, /pm/punch_recesses, /pm/punch_ribbing</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>wt_2</t>
+          <t>mm_2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>/wt/pick_up_and_transport</t>
+          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pm_1</t>
+          <t>wt_2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>204</v>
+        <v>330</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>/pm/punch_gill, /pm/punch_recesses, /pm/punch_ribbing</t>
+          <t>/wt/pick_up_and_transport</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hw_1</t>
+          <t>mm_1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>522</v>
+        <v>576</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>/hw/human_review</t>
+          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ov_1</t>
+          <t>hw_1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>612</v>
+        <v>522</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>/ov/burn, /ov/temper</t>
+          <t>/hw/human_review</t>
         </is>
       </c>
     </row>
@@ -585,126 +585,126 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dm_2</t>
+          <t>sm_2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>177</v>
+        <v>309</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>/dm/cylindrical_drill, /dm/drill, /dm/lower</t>
+          <t>/sm/sort, /sm/transport</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>wt_1</t>
+          <t>vgr_2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>447</v>
+        <v>885</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>/wt/pick_up_and_transport</t>
+          <t>/vgr/pick_up_and_transport</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ov_2</t>
+          <t>hbw_2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>330</v>
+        <v>1581</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>/ov/burn</t>
+          <t>/hbw/store_empty_bucket, /hbw/unload</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hbw_1</t>
+          <t>vgr_1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>873</v>
+        <v>1866</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>/hbw/get_empty_bucket, /hbw/store, /hbw/store_empty_bucket, /hbw/unload</t>
+          <t>/vgr/pick_up_and_transport</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sm_2</t>
+          <t>wt_1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>309</v>
+        <v>447</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>/sm/sort, /sm/transport</t>
+          <t>/wt/pick_up_and_transport</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hbw_2</t>
+          <t>ov_1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1581</v>
+        <v>612</v>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>/hbw/store_empty_bucket, /hbw/unload</t>
+          <t>/ov/burn, /ov/temper</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>vgr_2</t>
+          <t>dm_2</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>885</v>
+        <v>177</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>/vgr/pick_up_and_transport</t>
+          <t>/dm/cylindrical_drill, /dm/drill, /dm/lower</t>
         </is>
       </c>
     </row>

--- a/Data/tables/resources_info.xlsx
+++ b/Data/tables/resources_info.xlsx
@@ -441,79 +441,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hbw_1</t>
+          <t>sm_2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>873</v>
+        <v>309</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>/hbw/get_empty_bucket, /hbw/store, /hbw/store_empty_bucket, /hbw/unload</t>
+          <t>/sm/sort, /sm/transport</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ov_2</t>
+          <t>pm_1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>330</v>
+        <v>204</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>/ov/burn</t>
+          <t>/pm/punch_gill, /pm/punch_recesses, /pm/punch_ribbing</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pm_1</t>
+          <t>mm_2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>204</v>
+        <v>381</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>/pm/punch_gill, /pm/punch_recesses, /pm/punch_ribbing</t>
+          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mm_2</t>
+          <t>vgr_1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>381</v>
+        <v>1866</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
+          <t>/vgr/pick_up_and_transport</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>wt_2</t>
+          <t>ov_2</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -524,187 +524,187 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>/wt/pick_up_and_transport</t>
+          <t>/ov/burn</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mm_1</t>
+          <t>wt_1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>576</v>
+        <v>447</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
+          <t>/wt/pick_up_and_transport</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hw_1</t>
+          <t>hbw_1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>522</v>
+        <v>873</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>/hw/human_review</t>
+          <t>/hbw/get_empty_bucket, /hbw/store, /hbw/store_empty_bucket, /hbw/unload</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sm_1</t>
+          <t>wt_2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>378</v>
+        <v>330</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>/sm/sort, /sm/transport</t>
+          <t>/wt/pick_up_and_transport</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sm_2</t>
+          <t>dm_2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>309</v>
+        <v>177</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>/sm/sort, /sm/transport</t>
+          <t>/dm/cylindrical_drill, /dm/drill, /dm/lower</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vgr_2</t>
+          <t>hw_1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>885</v>
+        <v>522</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>/vgr/pick_up_and_transport</t>
+          <t>/hw/human_review</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hbw_2</t>
+          <t>sm_1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1581</v>
+        <v>378</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>/hbw/store_empty_bucket, /hbw/unload</t>
+          <t>/sm/sort, /sm/transport</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>vgr_1</t>
+          <t>hbw_2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1866</v>
+        <v>1581</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>/vgr/pick_up_and_transport</t>
+          <t>/hbw/store_empty_bucket, /hbw/unload</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wt_1</t>
+          <t>ov_1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>447</v>
+        <v>612</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>/wt/pick_up_and_transport</t>
+          <t>/ov/burn, /ov/temper</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ov_1</t>
+          <t>mm_1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>612</v>
+        <v>576</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>/ov/burn, /ov/temper</t>
+          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dm_2</t>
+          <t>vgr_2</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>177</v>
+        <v>885</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>/dm/cylindrical_drill, /dm/drill, /dm/lower</t>
+          <t>/vgr/pick_up_and_transport</t>
         </is>
       </c>
     </row>

--- a/Data/tables/resources_info.xlsx
+++ b/Data/tables/resources_info.xlsx
@@ -441,133 +441,133 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sm_2</t>
+          <t>vgr_1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>309</v>
+        <v>1866</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>/sm/sort, /sm/transport</t>
+          <t>/vgr/pick_up_and_transport</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pm_1</t>
+          <t>hbw_1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>204</v>
+        <v>873</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>/pm/punch_gill, /pm/punch_recesses, /pm/punch_ribbing</t>
+          <t>/hbw/get_empty_bucket, /hbw/store, /hbw/store_empty_bucket, /hbw/unload</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mm_2</t>
+          <t>hw_1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>381</v>
+        <v>522</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
+          <t>/hw/human_review</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>vgr_1</t>
+          <t>wt_2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1866</v>
+        <v>330</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>/vgr/pick_up_and_transport</t>
+          <t>/wt/pick_up_and_transport</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ov_2</t>
+          <t>sm_2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>/ov/burn</t>
+          <t>/sm/sort, /sm/transport</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>wt_1</t>
+          <t>dm_2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>447</v>
+        <v>177</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>/wt/pick_up_and_transport</t>
+          <t>/dm/cylindrical_drill, /dm/drill, /dm/lower</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hbw_1</t>
+          <t>sm_1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>873</v>
+        <v>378</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>/hbw/get_empty_bucket, /hbw/store, /hbw/store_empty_bucket, /hbw/unload</t>
+          <t>/sm/sort, /sm/transport</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>wt_2</t>
+          <t>ov_2</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -578,79 +578,79 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>/wt/pick_up_and_transport</t>
+          <t>/ov/burn</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dm_2</t>
+          <t>vgr_2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>177</v>
+        <v>885</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>/dm/cylindrical_drill, /dm/drill, /dm/lower</t>
+          <t>/vgr/pick_up_and_transport</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hw_1</t>
+          <t>mm_1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>522</v>
+        <v>576</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>/hw/human_review</t>
+          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sm_1</t>
+          <t>mm_2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>/sm/sort, /sm/transport</t>
+          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hbw_2</t>
+          <t>pm_1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1581</v>
+        <v>204</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>/hbw/store_empty_bucket, /hbw/unload</t>
+          <t>/pm/punch_gill, /pm/punch_recesses, /pm/punch_ribbing</t>
         </is>
       </c>
     </row>
@@ -675,36 +675,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mm_1</t>
+          <t>hbw_2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>576</v>
+        <v>1581</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
+          <t>/hbw/store_empty_bucket, /hbw/unload</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>vgr_2</t>
+          <t>wt_1</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>885</v>
+        <v>447</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>/vgr/pick_up_and_transport</t>
+          <t>/wt/pick_up_and_transport</t>
         </is>
       </c>
     </row>

--- a/Data/tables/resources_info.xlsx
+++ b/Data/tables/resources_info.xlsx
@@ -441,72 +441,72 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>vgr_1</t>
+          <t>hbw_2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1866</v>
+        <v>1581</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>/vgr/pick_up_and_transport</t>
+          <t>/hbw/store_empty_bucket, /hbw/unload</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hbw_1</t>
+          <t>dm_2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>873</v>
+        <v>177</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>/hbw/get_empty_bucket, /hbw/store, /hbw/store_empty_bucket, /hbw/unload</t>
+          <t>/dm/cylindrical_drill, /dm/drill, /dm/lower</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hw_1</t>
+          <t>sm_1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>522</v>
+        <v>378</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>/hw/human_review</t>
+          <t>/sm/sort, /sm/transport</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>wt_2</t>
+          <t>hbw_1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>330</v>
+        <v>873</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>/wt/pick_up_and_transport</t>
+          <t>/hbw/get_empty_bucket, /hbw/store, /hbw/store_empty_bucket, /hbw/unload</t>
         </is>
       </c>
     </row>
@@ -531,65 +531,65 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dm_2</t>
+          <t>mm_1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>177</v>
+        <v>576</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>/dm/cylindrical_drill, /dm/drill, /dm/lower</t>
+          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sm_1</t>
+          <t>pm_1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>378</v>
+        <v>204</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>/sm/sort, /sm/transport</t>
+          <t>/pm/punch_gill, /pm/punch_recesses, /pm/punch_ribbing</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ov_2</t>
+          <t>ov_1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>330</v>
+        <v>612</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>/ov/burn</t>
+          <t>/ov/burn, /ov/temper</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>vgr_2</t>
+          <t>vgr_1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>885</v>
+        <v>1866</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -603,108 +603,108 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mm_1</t>
+          <t>wt_2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>576</v>
+        <v>330</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
+          <t>/wt/pick_up_and_transport</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mm_2</t>
+          <t>wt_1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>381</v>
+        <v>447</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
+          <t>/wt/pick_up_and_transport</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pm_1</t>
+          <t>mm_2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>204</v>
+        <v>381</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>/pm/punch_gill, /pm/punch_recesses, /pm/punch_ribbing</t>
+          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ov_1</t>
+          <t>ov_2</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>612</v>
+        <v>330</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>/ov/burn, /ov/temper</t>
+          <t>/ov/burn</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hbw_2</t>
+          <t>hw_1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1581</v>
+        <v>522</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>/hbw/store_empty_bucket, /hbw/unload</t>
+          <t>/hw/human_review</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>wt_1</t>
+          <t>vgr_2</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>447</v>
+        <v>885</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>/wt/pick_up_and_transport</t>
+          <t>/vgr/pick_up_and_transport</t>
         </is>
       </c>
     </row>

--- a/Data/tables/resources_info.xlsx
+++ b/Data/tables/resources_info.xlsx
@@ -441,270 +441,270 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hbw_2</t>
+          <t>wt_1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1581</v>
+        <v>447</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>/hbw/store_empty_bucket, /hbw/unload</t>
+          <t>/wt/pick_up_and_transport</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dm_2</t>
+          <t>mm_1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>177</v>
+        <v>576</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>/dm/cylindrical_drill, /dm/drill, /dm/lower</t>
+          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sm_1</t>
+          <t>hw_1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>378</v>
+        <v>522</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>/sm/sort, /sm/transport</t>
+          <t>/hw/human_review</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hbw_1</t>
+          <t>ov_2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>873</v>
+        <v>330</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>/hbw/get_empty_bucket, /hbw/store, /hbw/store_empty_bucket, /hbw/unload</t>
+          <t>/ov/burn</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sm_2</t>
+          <t>wt_2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>/sm/sort, /sm/transport</t>
+          <t>/wt/pick_up_and_transport</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mm_1</t>
+          <t>vgr_2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>576</v>
+        <v>885</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
+          <t>/vgr/pick_up_and_transport</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pm_1</t>
+          <t>hbw_2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>204</v>
+        <v>1581</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>/pm/punch_gill, /pm/punch_recesses, /pm/punch_ribbing</t>
+          <t>/hbw/store_empty_bucket, /hbw/unload</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ov_1</t>
+          <t>sm_2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>612</v>
+        <v>309</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>/ov/burn, /ov/temper</t>
+          <t>/sm/sort, /sm/transport</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>vgr_1</t>
+          <t>sm_1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1866</v>
+        <v>378</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>/vgr/pick_up_and_transport</t>
+          <t>/sm/sort, /sm/transport</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>wt_2</t>
+          <t>dm_2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>330</v>
+        <v>177</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>/wt/pick_up_and_transport</t>
+          <t>/dm/cylindrical_drill, /dm/drill, /dm/lower</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>wt_1</t>
+          <t>ov_1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>447</v>
+        <v>612</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>/wt/pick_up_and_transport</t>
+          <t>/ov/burn, /ov/temper</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mm_2</t>
+          <t>pm_1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>381</v>
+        <v>204</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
+          <t>/pm/punch_gill, /pm/punch_recesses, /pm/punch_ribbing</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ov_2</t>
+          <t>vgr_1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>330</v>
+        <v>1866</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>/ov/burn</t>
+          <t>/vgr/pick_up_and_transport</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hw_1</t>
+          <t>mm_2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>522</v>
+        <v>381</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>/hw/human_review</t>
+          <t>/mm/deburr, /mm/drill, /mm/mill, /mm/transport_from_to</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>vgr_2</t>
+          <t>hbw_1</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>885</v>
+        <v>873</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>/vgr/pick_up_and_transport</t>
+          <t>/hbw/get_empty_bucket, /hbw/store, /hbw/store_empty_bucket, /hbw/unload</t>
         </is>
       </c>
     </row>
